--- a/Outputs/Scenarios/PtX_demand_DE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DE_Electrification.xlsx
@@ -507,7 +507,7 @@
         <v>0.1261598424973813</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0528087892306123</v>
+        <v>0.05280878923061231</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0.995825433828615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009184739703939499</v>
+        <v>0.009184739703939501</v>
       </c>
       <c r="H11" t="n">
         <v>0.1682123658973846</v>
@@ -1555,7 +1555,7 @@
         <v>0.03268628793279557</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05823116444812829</v>
+        <v>0.05823116444812828</v>
       </c>
     </row>
     <row r="31">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.05823116444812829</v>
+        <v>0.05823116444812828</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_DE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DE_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.02207968662960989</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01001803198324663</v>
+        <v>0.01269466743197721</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001669671997207771</v>
+        <v>0.002008959093482734</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.006678687988831085</v>
+        <v>0.008035836373930938</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01001803198324663</v>
+        <v>0.008035836373930938</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.001769470204155065</v>
       </c>
       <c r="K24" t="n">
-        <v>0.01469299875455726</v>
+        <v>0.01442496095514863</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.01071060686839585</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1349660160641547</v>
+        <v>0.1325038914464986</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>0.0003181309096915025</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001669671997207771</v>
+        <v>0.002008959093482734</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.03268628793279557</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05823116444812828</v>
+        <v>0.06764453158357187</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.009705194074688049</v>
+        <v>0.0107048961760813</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0388207762987522</v>
+        <v>0.04281958470432522</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.05823116444812828</v>
+        <v>0.04281958470432522</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.001720330943831346</v>
       </c>
       <c r="K42" t="n">
-        <v>0.009705194074688049</v>
+        <v>0.0107048961760813</v>
       </c>
     </row>
     <row r="43">
